--- a/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,262 +771,152 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Date Offset</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
+          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Onboarding Date Offset</t>
+          <t>Onboarding Map</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHKANS7965H6AX88QT0E48QG</t>
+          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKANS7965H6AX88QT0E48QG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Offboarding Date Offset</t>
+          <t>Offboarding Map</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHKANWAXRFS6DFAN1MWCJCK2</t>
+          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKANWAXRFS6DFAN1MWCJCK2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Debug Settings</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KHKBGVW1RE1DJZYENEJ6SM78</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBGVW1RE1DJZYENEJ6SM78</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Additional Options</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Onboarding Map</t>
+          <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Offboarding Map</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>H3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Schedule</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>H2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Execute Integration</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Additional Options</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Update the Integration to the Latest Version</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,51 +771,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Logging</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Onboarding Map</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Offboarding Map</t>
+          <t>Onboarding Map</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,63 +825,63 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Offboarding Map</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -891,32 +891,54 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -776,24 +776,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
+          <t>h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKAHS0RPY90Y3MTKX7D18KY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKAY5WRHT5HMSHZHYHR83QN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insight Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,63 +803,63 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>h_01KJABQZGT4TQQN6A1V0BNHYHT</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KJABQZGT4TQQN6A1V0BNHYHT</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Onboarding Map</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>h_01KJC8VW4WATPSB1M1AMK3G979</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KJC8VW4WATPSB1M1AMK3G979</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Offboarding Map</t>
+          <t>Reporting Settings</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>h_01KJCB73G09AAP2EPVKAJC57MP</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KJCB73G09AAP2EPVKAJC57MP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,76 +869,142 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKB5JY6TY3YJQRG433GPA14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Onboarding Map</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKEQDDTMMB1CCCQRVRM1E</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Offboarding Map</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKBKHBP49K206ZXCYR1NSCH</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/headings.xlsx
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Manage Hires</t>
+          <t>Onboarding Tickets</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Onboarding Tickets Generation</t>
+          <t>Onboarding Tickets Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -683,12 +683,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Mover Tickets</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -705,51 +705,51 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Manage Terminations</t>
+          <t>Mover Ticket Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KHKACRS1SACB85DEV28Y1RTF</t>
+          <t>h_01KJQ0VZAHX5ETB0TMYD633G59</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKACRS1SACB85DEV28Y1RTF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KJQ0VZAHX5ETB0TMYD633G59</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Offboarding Tickets Generation</t>
+          <t>Offboarding Tickets</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KHKADH0CYDDWB04HGJNJNS4F</t>
+          <t>h_01KHKACRS1SACB85DEV28Y1RTF</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKADH0CYDDWB04HGJNJNS4F</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKACRS1SACB85DEV28Y1RTF</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Correlation Settings</t>
+          <t>Offboarding Tickets Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -759,12 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KHKADH0CMR3ZG14R5C65TJTW</t>
+          <t>h_01KHKADH0CYDDWB04HGJNJNS4F</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKADH0CMR3ZG14R5C65TJTW</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KHKADH0CYDDWB04HGJNJNS4F</t>
         </is>
       </c>
     </row>

--- a/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/headings.xlsx
+++ b/site/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,7 +639,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Onboarding Tickets</t>
+          <t>Joiner Tickets</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Onboarding Tickets Settings</t>
+          <t>JoinerTickets Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Offboarding Tickets</t>
+          <t>Leaver Tickets</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Offboarding Tickets Settings</t>
+          <t>Leaver Tickets Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Onboarding Map</t>
+          <t>Joiner</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -903,7 +903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Offboarding Map</t>
+          <t>Mover</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -925,51 +925,51 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Leaver</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>h_01KJQAXTQKX4H8JD0KEMQ4G700</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KJQAXTQKX4H8JD0KEMQ4G700</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K04J6RRA21B3QX6Q3EPK80JN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Execute Integration</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,32 +979,54 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/ADP-Workforce-Now-to-ManageEngine-ServiceDesk-Plus-for-Cloud-Integration-Guide-Draft/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
